--- a/samples/openpyxlwings_sample.xlsx
+++ b/samples/openpyxlwings_sample.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="QuickReadWrite" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BorderedTable" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BrokenBorder" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AmountHeaders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BrokenBorder" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -931,6 +932,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>見出し値から検出する罫線テーブル</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>header1/header2 を固定見出し、amount を値領域の見出しとして検出できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>header1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>header2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>amount forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>header_col1</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>header2_col1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>header_col2</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>header2_col2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>header_col3</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>header2_col3</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Manual test:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>table = book.get_bordered_table_by_header("AmountHeaders", ["header1", "header2"], value_header_contains="amount")</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>print(table.row_headers); print(table.column_headers); print(table.data)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/samples/openpyxlwings_sample.xlsx
+++ b/samples/openpyxlwings_sample.xlsx
@@ -807,7 +807,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C5など、表内のセルを起点に get_bordered_table() を試せます。</t>
+          <t>表の左上セル（B4）を起点に get_bordered_table() を試せます。</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>table = book.get_bordered_table("BorderedTable", row=5, column=3, header_rows=2, header_columns=1)</t>
+          <t>table = book.get_bordered_table("BorderedTable", row=4, column=2, header_rows=2, header_columns=1)</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>table = book.get_bordered_table_by_header("AmountHeaders", ["header1", "header2"], value_header_contains="amount")</t>
+          <t>table = book.get_bordered_table("AmountHeaders", header_values=["header1", "header2"], value_header_contains="amount")</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>内部罫線が欠けているため、get_bordered_table() は例外を出す想定です。</t>
+          <t>内部罫線が欠けていても、左上セル起点の get_bordered_table() で読み取れます。</t>
         </is>
       </c>
     </row>
